--- a/Shiny/Datos limpios/pricing_diario_sorgo_2025.xlsx
+++ b/Shiny/Datos limpios/pricing_diario_sorgo_2025.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K221"/>
+  <dimension ref="A1:K241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -8341,16 +8341,16 @@
         <v>45947</v>
       </c>
       <c r="B216">
-        <v>18404.82</v>
+        <v>17904.82</v>
       </c>
       <c r="C216">
         <v>0</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E216">
-        <v>18404.82</v>
+        <v>17404.82</v>
       </c>
       <c r="F216">
         <v>60.13</v>
@@ -8365,7 +8365,7 @@
         <v>60.13</v>
       </c>
       <c r="J216">
-        <v>18464.95</v>
+        <v>17464.95</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -8553,6 +8553,746 @@
         <v>684.49</v>
       </c>
       <c r="K221" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2">
+        <v>45957</v>
+      </c>
+      <c r="B222">
+        <v>775</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222">
+        <v>775</v>
+      </c>
+      <c r="F222">
+        <v>514.08</v>
+      </c>
+      <c r="G222">
+        <v>0</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222">
+        <v>514.08</v>
+      </c>
+      <c r="J222">
+        <v>1289.08</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B223">
+        <v>1520.12</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+      <c r="E223">
+        <v>1520.12</v>
+      </c>
+      <c r="F223">
+        <v>36</v>
+      </c>
+      <c r="G223">
+        <v>0</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+      <c r="I223">
+        <v>36</v>
+      </c>
+      <c r="J223">
+        <v>1556.12</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B224">
+        <v>164.4</v>
+      </c>
+      <c r="C224">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="D224">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="E224">
+        <v>164.4</v>
+      </c>
+      <c r="F224">
+        <v>1500</v>
+      </c>
+      <c r="G224">
+        <v>0</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+      <c r="I224">
+        <v>1500</v>
+      </c>
+      <c r="J224">
+        <v>1664.4</v>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B225">
+        <v>561.78</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>561.78</v>
+      </c>
+      <c r="F225">
+        <v>330.28</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225">
+        <v>330.28</v>
+      </c>
+      <c r="J225">
+        <v>892.0599999999999</v>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B226">
+        <v>1686.36</v>
+      </c>
+      <c r="C226">
+        <v>59.08</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>1745.44</v>
+      </c>
+      <c r="F226">
+        <v>6214.9</v>
+      </c>
+      <c r="G226">
+        <v>0</v>
+      </c>
+      <c r="H226">
+        <v>300</v>
+      </c>
+      <c r="I226">
+        <v>5914.9</v>
+      </c>
+      <c r="J226">
+        <v>7660.339999999999</v>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B227">
+        <v>579.28</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <v>579.28</v>
+      </c>
+      <c r="F227">
+        <v>2120</v>
+      </c>
+      <c r="G227">
+        <v>0</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+      <c r="I227">
+        <v>2120</v>
+      </c>
+      <c r="J227">
+        <v>2699.28</v>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B228">
+        <v>895.99</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>895.99</v>
+      </c>
+      <c r="F228">
+        <v>814.16</v>
+      </c>
+      <c r="G228">
+        <v>0</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>814.16</v>
+      </c>
+      <c r="J228">
+        <v>1710.15</v>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B229">
+        <v>1036.88</v>
+      </c>
+      <c r="C229">
+        <v>500</v>
+      </c>
+      <c r="D229">
+        <v>30</v>
+      </c>
+      <c r="E229">
+        <v>1506.88</v>
+      </c>
+      <c r="F229">
+        <v>3121.38</v>
+      </c>
+      <c r="G229">
+        <v>0</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229">
+        <v>3121.38</v>
+      </c>
+      <c r="J229">
+        <v>4628.26</v>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B230">
+        <v>804.12</v>
+      </c>
+      <c r="C230">
+        <v>11.44</v>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230">
+        <v>815.5600000000001</v>
+      </c>
+      <c r="F230">
+        <v>1130.72</v>
+      </c>
+      <c r="G230">
+        <v>0</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>1130.72</v>
+      </c>
+      <c r="J230">
+        <v>1946.28</v>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B231">
+        <v>1359.89</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+      <c r="E231">
+        <v>1359.89</v>
+      </c>
+      <c r="F231">
+        <v>849.1900000000001</v>
+      </c>
+      <c r="G231">
+        <v>0</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+      <c r="I231">
+        <v>849.1900000000001</v>
+      </c>
+      <c r="J231">
+        <v>2209.08</v>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B232">
+        <v>1321.14</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>1321.14</v>
+      </c>
+      <c r="F232">
+        <v>700</v>
+      </c>
+      <c r="G232">
+        <v>0</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+      <c r="I232">
+        <v>700</v>
+      </c>
+      <c r="J232">
+        <v>2021.14</v>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B233">
+        <v>797.55</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+      <c r="E233">
+        <v>797.55</v>
+      </c>
+      <c r="F233">
+        <v>640</v>
+      </c>
+      <c r="G233">
+        <v>0</v>
+      </c>
+      <c r="H233">
+        <v>0</v>
+      </c>
+      <c r="I233">
+        <v>640</v>
+      </c>
+      <c r="J233">
+        <v>1437.55</v>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B234">
+        <v>641.79</v>
+      </c>
+      <c r="C234">
+        <v>106.67</v>
+      </c>
+      <c r="D234">
+        <v>0</v>
+      </c>
+      <c r="E234">
+        <v>748.4599999999999</v>
+      </c>
+      <c r="F234">
+        <v>330</v>
+      </c>
+      <c r="G234">
+        <v>0</v>
+      </c>
+      <c r="H234">
+        <v>0</v>
+      </c>
+      <c r="I234">
+        <v>330</v>
+      </c>
+      <c r="J234">
+        <v>1078.46</v>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B235">
+        <v>1177.18</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+      <c r="E235">
+        <v>1177.18</v>
+      </c>
+      <c r="F235">
+        <v>704.3</v>
+      </c>
+      <c r="G235">
+        <v>0</v>
+      </c>
+      <c r="H235">
+        <v>0</v>
+      </c>
+      <c r="I235">
+        <v>704.3</v>
+      </c>
+      <c r="J235">
+        <v>1881.48</v>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B236">
+        <v>847.15</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>0</v>
+      </c>
+      <c r="E236">
+        <v>847.15</v>
+      </c>
+      <c r="F236">
+        <v>330</v>
+      </c>
+      <c r="G236">
+        <v>0</v>
+      </c>
+      <c r="H236">
+        <v>0</v>
+      </c>
+      <c r="I236">
+        <v>330</v>
+      </c>
+      <c r="J236">
+        <v>1177.15</v>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B237">
+        <v>145</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237">
+        <v>145</v>
+      </c>
+      <c r="F237">
+        <v>0</v>
+      </c>
+      <c r="G237">
+        <v>0</v>
+      </c>
+      <c r="H237">
+        <v>0</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>145</v>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B238">
+        <v>473.95</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>0</v>
+      </c>
+      <c r="E238">
+        <v>473.95</v>
+      </c>
+      <c r="F238">
+        <v>270</v>
+      </c>
+      <c r="G238">
+        <v>0</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+      <c r="I238">
+        <v>270</v>
+      </c>
+      <c r="J238">
+        <v>743.95</v>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B239">
+        <v>420</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+      <c r="E239">
+        <v>420</v>
+      </c>
+      <c r="F239">
+        <v>60</v>
+      </c>
+      <c r="G239">
+        <v>0</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239">
+        <v>60</v>
+      </c>
+      <c r="J239">
+        <v>480</v>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B240">
+        <v>332.46</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+      <c r="E240">
+        <v>332.46</v>
+      </c>
+      <c r="F240">
+        <v>130</v>
+      </c>
+      <c r="G240">
+        <v>0</v>
+      </c>
+      <c r="H240">
+        <v>0</v>
+      </c>
+      <c r="I240">
+        <v>130</v>
+      </c>
+      <c r="J240">
+        <v>462.46</v>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>SORGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B241">
+        <v>1364.39</v>
+      </c>
+      <c r="C241">
+        <v>120</v>
+      </c>
+      <c r="D241">
+        <v>0</v>
+      </c>
+      <c r="E241">
+        <v>1484.39</v>
+      </c>
+      <c r="F241">
+        <v>543.34</v>
+      </c>
+      <c r="G241">
+        <v>0</v>
+      </c>
+      <c r="H241">
+        <v>0</v>
+      </c>
+      <c r="I241">
+        <v>543.34</v>
+      </c>
+      <c r="J241">
+        <v>2027.73</v>
+      </c>
+      <c r="K241" t="inlineStr">
         <is>
           <t>SORGO</t>
         </is>
